--- a/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -73,31 +73,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>REYLI</t>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
   </si>
   <si>
     <t>MONICA</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
   </si>
 </sst>
 </file>
@@ -498,16 +522,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -521,16 +548,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.76000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -586,7 +616,7 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -609,7 +639,7 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -668,16 +698,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,16 +724,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.76000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +746,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -742,16 +778,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920378</v>
+        <v>21330051920080</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -765,16 +801,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>18330051920296</v>
+        <v>21330051920094</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -788,16 +824,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>18330051920309</v>
+        <v>21330051920097</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -807,6 +843,75 @@
       </c>
       <c r="G4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920086</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>18330051920296</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -100,6 +100,9 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -116,6 +119,9 @@
   </si>
   <si>
     <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
   </si>
   <si>
     <t>FATIMA</t>
@@ -746,7 +752,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -787,7 +793,7 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -810,7 +816,7 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -833,7 +839,7 @@
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -856,7 +862,7 @@
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -870,39 +876,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920086</v>
+        <v>20330051920214</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>18330051920296</v>
+        <v>21330051920086</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -911,6 +917,29 @@
         <v>10</v>
       </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>18330051920296</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
@@ -100,15 +100,15 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
@@ -121,13 +121,13 @@
     <t>ANGEL DAVID</t>
   </si>
   <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
     <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
   </si>
 </sst>
 </file>
@@ -551,7 +551,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -560,13 +560,13 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -639,13 +639,13 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -727,7 +727,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -736,13 +736,13 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -876,10 +876,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920214</v>
+        <v>21330051920086</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
@@ -888,21 +888,21 @@
         <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920086</v>
+        <v>18330051920296</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>28</v>
@@ -922,10 +922,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>18330051920296</v>
+        <v>20330051920214</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
         <v>29</v>
@@ -934,10 +934,10 @@
         <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>1</v>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,58 +73,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
   </si>
   <si>
     <t>ALEJANDRA</t>
@@ -528,19 +480,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -554,19 +506,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -619,16 +571,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>72.5</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -642,16 +597,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>76.67</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -704,16 +662,16 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>97.5</v>
       </c>
       <c r="H2">
         <v>7.5</v>
@@ -730,19 +688,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -752,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -784,162 +742,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920080</v>
+        <v>20330051920214</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920094</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920097</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920102</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920086</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>18330051920296</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920214</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -73,10 +73,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
     <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RUBI</t>
   </si>
   <si>
     <t>ALEJANDRA</t>
@@ -710,7 +719,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -742,24 +751,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920214</v>
+        <v>21330051920107</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920214</v>
+      </c>
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,24 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
   </si>
 </sst>
 </file>
@@ -580,19 +562,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>72.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -606,19 +588,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>76.67</v>
+        <v>90</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -674,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -700,16 +682,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -749,52 +731,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920107</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920214</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
